--- a/artfynd/A 7847-2026 artfynd.xlsx
+++ b/artfynd/A 7847-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135039857</v>
+        <v>137306429</v>
       </c>
       <c r="B3" t="n">
-        <v>56930</v>
+        <v>9424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>101246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,20 +820,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagsätter, Hagsätter, Ög</t>
+          <t>Hagsätter, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569393</v>
+        <v>569445</v>
       </c>
       <c r="R3" t="n">
-        <v>6487131</v>
+        <v>6487200</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,29 +861,34 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Död hane. Inom området finns det gått om ekoxar. Förra året hittade jag fyra hanar och en hona under samma ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -887,16 +896,128 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Storm</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Storm</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137306429</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135039857</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hagsätter, Hagsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6487131</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Storm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Storm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135039857</t>
         </is>
@@ -906,6 +1027,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
